--- a/Convert_from_xlsx_to_Json/table_normalization/employment-table20.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/employment-table20.xlsx
@@ -1070,15 +1070,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1385,42 +1386,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="6">
         <v>2023</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="4"/>
+      <c r="A5" s="5"/>
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -1445,7 +1446,7 @@
       <c r="I5" t="s">
         <v>10</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -11626,18 +11627,18 @@
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A339" s="2" t="s">
+      <c r="A339" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="B339" s="2"/>
-      <c r="C339" s="2"/>
-      <c r="D339" s="2"/>
-      <c r="E339" s="2"/>
-      <c r="F339" s="2"/>
-      <c r="G339" s="2"/>
-      <c r="H339" s="2"/>
-      <c r="I339" s="2"/>
-      <c r="J339" s="2"/>
+      <c r="B339" s="4"/>
+      <c r="C339" s="4"/>
+      <c r="D339" s="4"/>
+      <c r="E339" s="4"/>
+      <c r="F339" s="4"/>
+      <c r="G339" s="4"/>
+      <c r="H339" s="4"/>
+      <c r="I339" s="4"/>
+      <c r="J339" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
